--- a/docs/09_Final_Report/ATPM_Group04_Final_Verification.xlsx
+++ b/docs/09_Final_Report/ATPM_Group04_Final_Verification.xlsx
@@ -1685,16 +1685,16 @@
         <v>100</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>87.0%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>78.5%</t>
+          <t>56.5% (52/92)</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Các nhánh I/O lỗi phần cứng hiếm gặp (fputs fail)</t>
+          <t>Các nhánh I/O lỗi phần cứng (fputs fail)</t>
         </is>
       </c>
     </row>
@@ -1718,21 +1718,21 @@
         <v>43</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>88.4%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>41.7% (10/24)</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Phủ toàn bộ import_stock, export_stock, find_product, inventory_free</t>
+          <t>Phủ import_stock, export_stock, find_product, inventory_free</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -1751,26 +1751,26 @@
         <v>135</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>76.3%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.3% (63/114)</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Phủ init, add_product, realloc growth, delete_product, find_product_by_id</t>
+          <t>Phủ product_list_init, add_product, realloc growth, delete_product, find_product_by_id</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Nhánh so sánh chuỗi không phân biệt hoa thường trong search_name</t>
+          <t>Nhánh so sánh chuỗi trong search_name</t>
         </is>
       </c>
     </row>
@@ -1784,26 +1784,26 @@
         <v>204</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>29.5% (33/112)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Phủ tính toán tóm tắt nhóm hàng cơ bản trong smoke test</t>
+          <t>Phủ tóm tắt nhóm hàng cơ bản trong smoke test</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Giao diện in ấn báo cáo bảng CLI rộng (không thuộc luồng kiểm toán cốt lõi)</t>
+          <t>Giao diện in báo cáo bảng CLI rộng</t>
         </is>
       </c>
     </row>
@@ -1817,26 +1817,26 @@
         <v>123</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>9.1% (10/110)</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Phủ safe_string_copy, trim_whitespace, parse helpers</t>
+          <t>Phủ safe_string_copy, trim_whitespace</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Các hàm tiện ích phụ trợ chuyển đổi chuỗi chưa gọi trong luồng nhập kho</t>
+          <t>Các tiện ích phụ trợ chuyển đổi chuỗi chưa gọi trong luồng nhập kho</t>
         </is>
       </c>
     </row>
@@ -1850,16 +1850,16 @@
         <v>165</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>32.7% (51/156)</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -1876,33 +1876,33 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>TỔNG CỘNG HỆ THỐNG</t>
+          <t>TỔNG CỘNG MÃ NGUỒN C (source/src/)</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
         <v>770</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>45.84%</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>36.02% (219/608)</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Tăng từ 36.4% lên 46.1% nhờ bổ sung 6 bộ test driver mô phỏng C</t>
+          <t>Tăng từ 36.4% ở Bước 3 lên 45.84% dòng và 36.02% nhánh nhờ 6 bộ C Simulator</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Các module report và menu CLI không bắt buộc phải phủ 100%</t>
+          <t>Module report và CLI không bắt buộc phủ 100% trong luồng kiểm toán</t>
         </is>
       </c>
     </row>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>2f6c9db41c36d472a21bd770cc230dd3fa30bd125ecbf310016dd97af624e2b2</t>
+          <t>5143f2411e505d59f265e0de2d267e3a10a746643c8bbf563c711c984da8d49c</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>FILE_NOT_FOUND</t>
+          <t>dfbbbb98a65e43f43beaac7bd1de27fcd247e661e8eedd29167b2ae9c3ec0497</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>FILE_NOT_FOUND</t>
+          <t>ede15569857acf940b67a5427dbeb6303a36323f679786b8531f724239448bf0</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>56d981bdf5319f2bbc2e1dec5d2a98fc85d6ffe63df15e9d9dedd69385a3bbf0</t>
+          <t>6a11e46767b0f5735f570535b6a554317c516a6ebad8687f3c49ee718721b653</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>2f0c3daadf55765aa334afea68879b25ee13f939e249c343734a590e21848582</t>
+          <t>cae882d1762aeae07479161e3e9de25f82b86cd004dbbae09cc7669e6b70f3a8</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>2085aa0ba93e906791890349350237d3d218e51ce3a3fa92ea0776512d833d27</t>
+          <t>edf96458c731f745615923155be5df14d5b1657932862be00971c87a7ee9fb3b</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">

--- a/docs/09_Final_Report/ATPM_Group04_Final_Verification.xlsx
+++ b/docs/09_Final_Report/ATPM_Group04_Final_Verification.xlsx
@@ -5121,7 +5121,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>add_product_to_list</t>
+          <t>add_product</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>add_product_to_list, free_product_list, inventory_free</t>
+          <t>add_product, product_list_free, inventory_free</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>find_product_by_id, add_product_to_list</t>
+          <t>find_product_by_id, add_product</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>import_product_stock, export_product_stock, update_stock</t>
+          <t>import_stock, export_stock, update_stock</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>add_product_to_list</t>
+          <t>add_product</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -6235,7 +6235,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>add_product_to_list</t>
+          <t>add_product</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>import_product_stock</t>
+          <t>import_stock</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>export_product_stock</t>
+          <t>export_stock</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>add_product_to_list</t>
+          <t>add_product</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>param == NULL -&gt; return STATUS_ERR_NULL_POINTER</t>
+          <t>param == NULL -&gt; return STATUS_ERR_NULL_PTR (-1)</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
